--- a/src/Verify.OpenXml.Tests/PrefixedNamespaceTests.OpenXmlSdkSpreadsheet.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/PrefixedNamespaceTests.OpenXmlSdkSpreadsheet.verified.xlsx
@@ -23,5 +23,6 @@
       </c>
     </row>
   </sheetData>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>